--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126331429</v>
+        <v>126330908</v>
       </c>
       <c r="B2" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464684</v>
+        <v>464517</v>
       </c>
       <c r="R2" t="n">
-        <v>6784961</v>
+        <v>6784987</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126330908</v>
+        <v>126331429</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464517</v>
+        <v>464684</v>
       </c>
       <c r="R3" t="n">
-        <v>6784987</v>
+        <v>6784961</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126330908</v>
+        <v>126331429</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464517</v>
+        <v>464684</v>
       </c>
       <c r="R2" t="n">
-        <v>6784987</v>
+        <v>6784961</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126331429</v>
+        <v>126330908</v>
       </c>
       <c r="B3" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464684</v>
+        <v>464517</v>
       </c>
       <c r="R3" t="n">
-        <v>6784961</v>
+        <v>6784987</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126331429</v>
+        <v>126330908</v>
       </c>
       <c r="B2" t="n">
-        <v>79009</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464684</v>
+        <v>464517</v>
       </c>
       <c r="R2" t="n">
-        <v>6784961</v>
+        <v>6784987</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126330908</v>
+        <v>126331429</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>79012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464517</v>
+        <v>464684</v>
       </c>
       <c r="R3" t="n">
-        <v>6784987</v>
+        <v>6784961</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>126330993</v>
       </c>
       <c r="B4" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126331162</v>
       </c>
       <c r="B6" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126330861</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126330962</v>
       </c>
       <c r="B8" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,6 +1351,3261 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126488981</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78738</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>464546</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6785003</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126487403</v>
+      </c>
+      <c r="B10" t="n">
+        <v>75075</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>464751</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6784883</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126487574</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>464728</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6784927</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126487283</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>464756</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6784907</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126488322</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>464571</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6785011</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126492867</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79012</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>185</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>464677</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6785000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126488330</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>464560</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6785003</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126488269</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78738</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>464700</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6784944</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126492770</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79012</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>185</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>464734</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6784881</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126489147</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>464662</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6784965</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126487945</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>464676</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6784994</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126488376</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78739</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>464662</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6784965</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126487034</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>464717</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6784886</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt i synfältet i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126492793</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79012</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>185</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>464714</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6784832</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126488129</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>464617</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6785002</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126487763</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79012</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>185</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>464717</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6784938</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126486167</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97245</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>464730</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6784881</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126488274</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>464590</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6785034</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126488973</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>464546</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6785003</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126488280</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>464590</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6785034</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126487646</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>464716</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6784948</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126488197</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>464601</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6785020</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126487777</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>464717</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6784938</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126492915</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79012</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>185</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>464647</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6785005</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126487998</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>464676</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6784994</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126487746</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>464684</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6784934</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126487352</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>464756</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6784907</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126487596</v>
+      </c>
+      <c r="B36" t="n">
+        <v>75075</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>464738</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6784934</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126487908</v>
+      </c>
+      <c r="B37" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>464652</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6784976</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126488040</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>464676</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6784994</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1787,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126488322</v>
+        <v>126492867</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79012</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,37 +1798,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464571</v>
+        <v>464677</v>
       </c>
       <c r="R13" t="n">
-        <v>6785011</v>
+        <v>6785000</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1855,24 +1858,14 @@
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i en radie av ca 50 meter</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1881,69 +1874,67 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126492867</v>
+        <v>126488330</v>
       </c>
       <c r="B14" t="n">
-        <v>79012</v>
+        <v>8447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464677</v>
+        <v>464560</v>
       </c>
       <c r="R14" t="n">
-        <v>6785000</v>
+        <v>6785003</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1970,14 +1961,19 @@
           <t>2025-07-07</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1986,67 +1982,66 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126488330</v>
+        <v>126488269</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>78738</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464560</v>
+        <v>464700</v>
       </c>
       <c r="R15" t="n">
-        <v>6785003</v>
+        <v>6784944</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,7 +2070,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2085,7 +2080,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2100,60 +2095,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126488269</v>
+        <v>126489147</v>
       </c>
       <c r="B16" t="n">
-        <v>78738</v>
+        <v>8447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464700</v>
+        <v>464662</v>
       </c>
       <c r="R16" t="n">
-        <v>6784944</v>
+        <v>6784965</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,50 +2325,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126489147</v>
+        <v>126487945</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464662</v>
+        <v>464676</v>
       </c>
       <c r="R18" t="n">
-        <v>6784965</v>
+        <v>6784994</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2425,22 +2425,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126487945</v>
+        <v>126488376</v>
       </c>
       <c r="B19" t="n">
-        <v>57654</v>
+        <v>78739</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2448,39 +2448,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464676</v>
+        <v>464662</v>
       </c>
       <c r="R19" t="n">
-        <v>6784994</v>
+        <v>6784965</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,7 +2507,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2522,7 +2517,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2537,22 +2532,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126488376</v>
+        <v>126487034</v>
       </c>
       <c r="B20" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2560,37 +2555,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464662</v>
+        <v>464717</v>
       </c>
       <c r="R20" t="n">
-        <v>6784965</v>
+        <v>6784886</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2619,7 +2614,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2629,7 +2624,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt i synfältet i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2644,22 +2644,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126487034</v>
+        <v>126492793</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79012</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2667,37 +2667,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464717</v>
+        <v>464714</v>
       </c>
       <c r="R21" t="n">
-        <v>6784886</v>
+        <v>6784832</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2724,24 +2727,14 @@
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt i synfältet i en radie av ca 50 meter</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,28 +2743,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126492793</v>
+        <v>126488129</v>
       </c>
       <c r="B22" t="n">
-        <v>79012</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2779,40 +2773,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464714</v>
+        <v>464617</v>
       </c>
       <c r="R22" t="n">
-        <v>6784832</v>
+        <v>6785002</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2839,14 +2830,19 @@
           <t>2025-07-07</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2855,29 +2851,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126488129</v>
+        <v>126487763</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>79012</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2885,34 +2880,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464617</v>
+        <v>464717</v>
       </c>
       <c r="R23" t="n">
-        <v>6785002</v>
+        <v>6784938</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,7 +2939,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2954,7 +2949,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2969,57 +2964,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126487763</v>
+        <v>126486167</v>
       </c>
       <c r="B24" t="n">
-        <v>79012</v>
+        <v>97245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464717</v>
+        <v>464730</v>
       </c>
       <c r="R24" t="n">
-        <v>6784938</v>
+        <v>6784881</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,7 +3046,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3061,7 +3056,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3076,57 +3071,62 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126486167</v>
+        <v>126488274</v>
       </c>
       <c r="B25" t="n">
-        <v>97245</v>
+        <v>57654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464730</v>
+        <v>464590</v>
       </c>
       <c r="R25" t="n">
-        <v>6784881</v>
+        <v>6785034</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126488274</v>
+        <v>126488973</v>
       </c>
       <c r="B26" t="n">
-        <v>57654</v>
+        <v>79598</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3206,39 +3206,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464590</v>
+        <v>464546</v>
       </c>
       <c r="R26" t="n">
-        <v>6785034</v>
+        <v>6785003</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3307,10 +3302,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126488973</v>
+        <v>126487646</v>
       </c>
       <c r="B27" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3318,21 +3313,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3342,10 +3337,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464546</v>
+        <v>464716</v>
       </c>
       <c r="R27" t="n">
-        <v>6785003</v>
+        <v>6784948</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3414,7 +3409,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126488280</v>
+        <v>126488197</v>
       </c>
       <c r="B28" t="n">
         <v>78980</v>
@@ -3449,10 +3444,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464590</v>
+        <v>464601</v>
       </c>
       <c r="R28" t="n">
-        <v>6785034</v>
+        <v>6785020</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3521,45 +3516,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126487646</v>
+        <v>126487777</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464716</v>
+        <v>464717</v>
       </c>
       <c r="R29" t="n">
-        <v>6784948</v>
+        <v>6784938</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3591,7 +3586,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3601,7 +3596,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3616,22 +3611,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126488197</v>
+        <v>126492915</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>79012</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3639,37 +3634,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464601</v>
+        <v>464647</v>
       </c>
       <c r="R30" t="n">
-        <v>6785020</v>
+        <v>6785005</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3696,19 +3694,14 @@
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3717,63 +3710,64 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126487777</v>
+        <v>126487998</v>
       </c>
       <c r="B31" t="n">
-        <v>8447</v>
+        <v>78980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464717</v>
+        <v>464676</v>
       </c>
       <c r="R31" t="n">
-        <v>6784938</v>
+        <v>6784994</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3805,7 +3799,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3815,7 +3809,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3830,22 +3824,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126492915</v>
+        <v>126487746</v>
       </c>
       <c r="B32" t="n">
-        <v>79012</v>
+        <v>78980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3853,40 +3847,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464647</v>
+        <v>464684</v>
       </c>
       <c r="R32" t="n">
-        <v>6785005</v>
+        <v>6784934</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3913,14 +3904,24 @@
           <t>2025-07-07</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3929,29 +3930,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126487998</v>
+        <v>126487352</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3959,37 +3959,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464676</v>
+        <v>464756</v>
       </c>
       <c r="R33" t="n">
-        <v>6784994</v>
+        <v>6784907</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4018,7 +4023,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4028,7 +4033,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4043,22 +4048,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126487746</v>
+        <v>126487596</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>75075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4066,21 +4071,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4090,13 +4095,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464684</v>
+        <v>464738</v>
       </c>
       <c r="R34" t="n">
         <v>6784934</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4136,11 +4141,6 @@
       <c r="AB34" t="inlineStr">
         <is>
           <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4167,50 +4167,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126487352</v>
+        <v>126487908</v>
       </c>
       <c r="B35" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464756</v>
+        <v>464652</v>
       </c>
       <c r="R35" t="n">
-        <v>6784907</v>
+        <v>6784976</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4242,7 +4246,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4252,7 +4256,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4279,32 +4283,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126487596</v>
+        <v>126488040</v>
       </c>
       <c r="B36" t="n">
-        <v>75075</v>
+        <v>8447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4314,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464738</v>
+        <v>464676</v>
       </c>
       <c r="R36" t="n">
-        <v>6784934</v>
+        <v>6784994</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,229 +4387,6 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>126487908</v>
-      </c>
-      <c r="B37" t="n">
-        <v>8447</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Kölbron, Kölbron, Dlr</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>464652</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6784976</v>
-      </c>
-      <c r="S37" t="n">
-        <v>20</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Våmhus</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Bengt Oldhammer</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>126488040</v>
-      </c>
-      <c r="B38" t="n">
-        <v>8447</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Kölbron, Dlr</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>464676</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6784994</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Våmhus</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -1893,48 +1893,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126488330</v>
+        <v>126492770</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>79012</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464560</v>
+        <v>464734</v>
       </c>
       <c r="R14" t="n">
-        <v>6785003</v>
+        <v>6784881</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1961,19 +1964,14 @@
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1982,18 +1980,19 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2107,7 +2106,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126489147</v>
+        <v>126488330</v>
       </c>
       <c r="B16" t="n">
         <v>8447</v>
@@ -2136,21 +2135,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464662</v>
+        <v>464560</v>
       </c>
       <c r="R16" t="n">
-        <v>6784965</v>
+        <v>6785003</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2182,7 +2176,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2192,7 +2186,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2207,63 +2201,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126492770</v>
+        <v>126489147</v>
       </c>
       <c r="B17" t="n">
-        <v>79012</v>
+        <v>8447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464734</v>
+        <v>464662</v>
       </c>
       <c r="R17" t="n">
-        <v>6784881</v>
+        <v>6784965</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2290,14 +2286,19 @@
           <t>2025-07-07</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2306,19 +2307,18 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126488129</v>
+        <v>126487763</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>79012</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2773,34 +2773,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464617</v>
+        <v>464717</v>
       </c>
       <c r="R22" t="n">
-        <v>6785002</v>
+        <v>6784938</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2857,22 +2857,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126487763</v>
+        <v>126488129</v>
       </c>
       <c r="B23" t="n">
-        <v>79012</v>
+        <v>78980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2880,34 +2880,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464717</v>
+        <v>464617</v>
       </c>
       <c r="R23" t="n">
-        <v>6784938</v>
+        <v>6785002</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2964,12 +2964,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3516,48 +3516,51 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126487777</v>
+        <v>126492915</v>
       </c>
       <c r="B29" t="n">
-        <v>8447</v>
+        <v>79012</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464717</v>
+        <v>464647</v>
       </c>
       <c r="R29" t="n">
-        <v>6784938</v>
+        <v>6785005</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3584,19 +3587,14 @@
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:58</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3605,69 +3603,67 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126492915</v>
+        <v>126487777</v>
       </c>
       <c r="B30" t="n">
-        <v>79012</v>
+        <v>8447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464647</v>
+        <v>464717</v>
       </c>
       <c r="R30" t="n">
-        <v>6785005</v>
+        <v>6784938</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3694,14 +3690,19 @@
           <t>2025-07-07</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3710,19 +3711,18 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126487352</v>
+        <v>126487596</v>
       </c>
       <c r="B33" t="n">
-        <v>57654</v>
+        <v>75075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3959,42 +3959,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464756</v>
+        <v>464738</v>
       </c>
       <c r="R33" t="n">
-        <v>6784907</v>
+        <v>6784934</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4023,7 +4018,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4033,7 +4028,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4048,22 +4043,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126487596</v>
+        <v>126487352</v>
       </c>
       <c r="B34" t="n">
-        <v>75075</v>
+        <v>57654</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4071,37 +4066,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464738</v>
+        <v>464756</v>
       </c>
       <c r="R34" t="n">
-        <v>6784934</v>
+        <v>6784907</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4155,12 +4155,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2869,32 +2869,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126488129</v>
+        <v>126486167</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>97245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464617</v>
+        <v>464730</v>
       </c>
       <c r="R23" t="n">
-        <v>6785002</v>
+        <v>6784881</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2976,32 +2976,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126486167</v>
+        <v>126488129</v>
       </c>
       <c r="B24" t="n">
-        <v>97245</v>
+        <v>78980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464730</v>
+        <v>464617</v>
       </c>
       <c r="R24" t="n">
-        <v>6784881</v>
+        <v>6785002</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4388,6 +4388,220 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126592039</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>464676</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6784794</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126591692</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>464670</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6784832</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4602,6 +4602,3047 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126602281</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>464586</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6784897</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126601759</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>464631</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6784825</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126602799</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>464491</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6784992</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Miljöbild med torraka och bandad tall med garnlav bakgrund</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126602311</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>464557</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6784931</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Miljöbild, torraka i bakgrund</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126602700</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>464491</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6784992</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Miljöbild med bandad tall</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126601678</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>464640</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6784813</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126601839</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>464633</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6784875</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126602177</v>
+      </c>
+      <c r="B46" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>464599</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6784887</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126602534</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>464528</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6784961</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126602338</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>464557</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6784931</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126601621</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>464649</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6784788</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126601811</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>464636</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6784853</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126601626</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78739</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>464649</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6784788</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126602170</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>464599</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6784887</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126601513</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>464648</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6784781</v>
+      </c>
+      <c r="S53" t="n">
+        <v>50</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126602285</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>464576</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6784903</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126601634</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>464649</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6784788</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126601664</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>464646</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6784794</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126602528</v>
+      </c>
+      <c r="B57" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>464528</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6784961</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Miljöbild, flera torrakor i bild</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126601871</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>464603</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6784862</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126602457</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>464554</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6784937</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Miljöbild, torraka i bakgrund</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126601794</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>464632</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6784828</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126591818</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>464670</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6784832</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126601826</v>
+      </c>
+      <c r="B62" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>464636</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6784853</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126601627</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78738</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>464649</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6784788</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126602005</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>464603</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6784862</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Miljöbild på hackhål/bohål</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126601623</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79569</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>464649</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6784788</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126602400</v>
+      </c>
+      <c r="B66" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>464557</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6784931</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4711,32 +4711,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126601759</v>
+        <v>126602799</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464631</v>
+        <v>464491</v>
       </c>
       <c r="R40" t="n">
-        <v>6784825</v>
+        <v>6784992</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,6 +4792,11 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Miljöbild med torraka och bandad tall med garnlav bakgrund</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,32 +4823,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126602799</v>
+        <v>126601759</v>
       </c>
       <c r="B41" t="n">
-        <v>8447</v>
+        <v>78980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4858,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464491</v>
+        <v>464631</v>
       </c>
       <c r="R41" t="n">
-        <v>6784992</v>
+        <v>6784825</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4899,11 +4904,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Miljöbild med torraka och bandad tall med garnlav bakgrund</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4930,7 +4930,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126602311</v>
+        <v>126602700</v>
       </c>
       <c r="B42" t="n">
         <v>78980</v>
@@ -4965,10 +4965,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464557</v>
+        <v>464491</v>
       </c>
       <c r="R42" t="n">
-        <v>6784931</v>
+        <v>6784992</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Miljöbild, torraka i bakgrund</t>
+          <t>Miljöbild med bandad tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5042,7 +5042,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126602700</v>
+        <v>126602311</v>
       </c>
       <c r="B43" t="n">
         <v>78980</v>
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464491</v>
+        <v>464557</v>
       </c>
       <c r="R43" t="n">
-        <v>6784992</v>
+        <v>6784931</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Miljöbild med bandad tall</t>
+          <t>Miljöbild, torraka i bakgrund</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6774,7 +6774,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126602457</v>
+        <v>126601794</v>
       </c>
       <c r="B59" t="n">
         <v>78980</v>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464554</v>
+        <v>464632</v>
       </c>
       <c r="R59" t="n">
-        <v>6784937</v>
+        <v>6784828</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6855,11 +6855,6 @@
       <c r="AB59" t="inlineStr">
         <is>
           <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Miljöbild, torraka i bakgrund</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6886,7 +6881,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126601794</v>
+        <v>126602457</v>
       </c>
       <c r="B60" t="n">
         <v>78980</v>
@@ -6921,10 +6916,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464632</v>
+        <v>464554</v>
       </c>
       <c r="R60" t="n">
-        <v>6784828</v>
+        <v>6784937</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6967,6 +6962,11 @@
       <c r="AB60" t="inlineStr">
         <is>
           <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Miljöbild, torraka i bakgrund</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7643,6 +7643,820 @@
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126636587</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>464649</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6784894</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126636762</v>
+      </c>
+      <c r="B68" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>464639</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6784932</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126636699</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>464636</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6784910</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126636748</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>464639</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6784929</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126636650</v>
+      </c>
+      <c r="B71" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>464649</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6784894</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126636724</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>464637</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6784913</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126636906</v>
+      </c>
+      <c r="B73" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>464593</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6785029</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126636895</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>464593</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6785029</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -4393,7 +4393,7 @@
         <v>126592039</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>126591692</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>126602281</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>126601759</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>126602700</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>126602311</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>126601839</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>126601678</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5475,10 +5475,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126602338</v>
+        <v>126602534</v>
       </c>
       <c r="B47" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5486,39 +5486,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464557</v>
+        <v>464528</v>
       </c>
       <c r="R47" t="n">
-        <v>6784931</v>
+        <v>6784961</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5561,11 +5556,6 @@
       <c r="AB47" t="inlineStr">
         <is>
           <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5592,10 +5582,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126602534</v>
+        <v>126602338</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5603,34 +5593,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464528</v>
+        <v>464557</v>
       </c>
       <c r="R48" t="n">
-        <v>6784961</v>
+        <v>6784931</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5673,6 +5668,11 @@
       <c r="AB48" t="inlineStr">
         <is>
           <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5699,10 +5699,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126601811</v>
+        <v>126601621</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5710,21 +5710,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464636</v>
+        <v>464649</v>
       </c>
       <c r="R49" t="n">
-        <v>6784853</v>
+        <v>6784788</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5806,10 +5806,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126602170</v>
+        <v>126601811</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5841,10 +5841,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464599</v>
+        <v>464636</v>
       </c>
       <c r="R50" t="n">
-        <v>6784887</v>
+        <v>6784853</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5913,10 +5913,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126601621</v>
+        <v>126602170</v>
       </c>
       <c r="B51" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5924,21 +5924,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464649</v>
+        <v>464599</v>
       </c>
       <c r="R51" t="n">
-        <v>6784788</v>
+        <v>6784887</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6023,7 +6023,7 @@
         <v>126601626</v>
       </c>
       <c r="B52" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>126602285</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>126601513</v>
       </c>
       <c r="B54" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6341,10 +6341,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126601634</v>
+        <v>126601664</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464649</v>
+        <v>464646</v>
       </c>
       <c r="R55" t="n">
-        <v>6784788</v>
+        <v>6784794</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6448,10 +6448,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126601664</v>
+        <v>126601634</v>
       </c>
       <c r="B56" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6483,10 +6483,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464646</v>
+        <v>464649</v>
       </c>
       <c r="R56" t="n">
-        <v>6784794</v>
+        <v>6784788</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6670,7 +6670,7 @@
         <v>126601794</v>
       </c>
       <c r="B58" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>126601871</v>
       </c>
       <c r="B59" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>126602457</v>
       </c>
       <c r="B60" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>126601627</v>
       </c>
       <c r="B61" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7324,32 +7324,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126601623</v>
+        <v>126602400</v>
       </c>
       <c r="B64" t="n">
-        <v>79569</v>
+        <v>8447</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7359,10 +7359,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464649</v>
+        <v>464557</v>
       </c>
       <c r="R64" t="n">
-        <v>6784788</v>
+        <v>6784931</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7431,32 +7431,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126602400</v>
+        <v>126601623</v>
       </c>
       <c r="B65" t="n">
-        <v>8447</v>
+        <v>79600</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464557</v>
+        <v>464649</v>
       </c>
       <c r="R65" t="n">
-        <v>6784931</v>
+        <v>6784788</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7541,7 +7541,7 @@
         <v>126636587</v>
       </c>
       <c r="B66" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>126636762</v>
       </c>
       <c r="B67" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>126636699</v>
       </c>
       <c r="B68" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>126636748</v>
       </c>
       <c r="B69" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>126636724</v>
       </c>
       <c r="B71" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>126636906</v>
       </c>
       <c r="B72" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>126591818</v>
       </c>
       <c r="B74" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -4393,7 +4393,7 @@
         <v>126592039</v>
       </c>
       <c r="B37" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>126591692</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>126602281</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4711,32 +4711,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126601759</v>
+        <v>126602799</v>
       </c>
       <c r="B40" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464631</v>
+        <v>464491</v>
       </c>
       <c r="R40" t="n">
-        <v>6784825</v>
+        <v>6784992</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,6 +4792,11 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Miljöbild med torraka och bandad tall med garnlav bakgrund</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,32 +4823,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126602799</v>
+        <v>126601759</v>
       </c>
       <c r="B41" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4858,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464491</v>
+        <v>464631</v>
       </c>
       <c r="R41" t="n">
-        <v>6784992</v>
+        <v>6784825</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4899,11 +4904,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Miljöbild med torraka och bandad tall med garnlav bakgrund</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4933,7 +4933,7 @@
         <v>126602700</v>
       </c>
       <c r="B42" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>126602311</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126601839</v>
+        <v>126601678</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464633</v>
+        <v>464640</v>
       </c>
       <c r="R44" t="n">
-        <v>6784875</v>
+        <v>6784813</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5261,10 +5261,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126601678</v>
+        <v>126601839</v>
       </c>
       <c r="B45" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464640</v>
+        <v>464633</v>
       </c>
       <c r="R45" t="n">
-        <v>6784813</v>
+        <v>6784875</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5478,7 +5478,7 @@
         <v>126602534</v>
       </c>
       <c r="B47" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>126601621</v>
       </c>
       <c r="B49" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>126601811</v>
       </c>
       <c r="B50" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>126602170</v>
       </c>
       <c r="B51" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>126601626</v>
       </c>
       <c r="B52" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>126602285</v>
       </c>
       <c r="B53" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>126601513</v>
       </c>
       <c r="B54" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>126601664</v>
       </c>
       <c r="B55" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>126601634</v>
       </c>
       <c r="B56" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>126601794</v>
       </c>
       <c r="B58" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>126601871</v>
       </c>
       <c r="B59" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>126602457</v>
       </c>
       <c r="B60" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>126601627</v>
       </c>
       <c r="B61" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>126601623</v>
       </c>
       <c r="B65" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>126636587</v>
       </c>
       <c r="B66" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>126636762</v>
       </c>
       <c r="B67" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>126636699</v>
       </c>
       <c r="B68" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>126636748</v>
       </c>
       <c r="B69" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>126636724</v>
       </c>
       <c r="B71" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>126636906</v>
       </c>
       <c r="B72" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>126591818</v>
       </c>
       <c r="B74" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -4711,32 +4711,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126602799</v>
+        <v>126601759</v>
       </c>
       <c r="B40" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464491</v>
+        <v>464631</v>
       </c>
       <c r="R40" t="n">
-        <v>6784992</v>
+        <v>6784825</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,11 +4792,6 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Miljöbild med torraka och bandad tall med garnlav bakgrund</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4823,32 +4818,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126601759</v>
+        <v>126602799</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4858,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464631</v>
+        <v>464491</v>
       </c>
       <c r="R41" t="n">
-        <v>6784825</v>
+        <v>6784992</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4904,6 +4899,11 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Miljöbild med torraka och bandad tall med garnlav bakgrund</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5475,10 +5475,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126602534</v>
+        <v>126602338</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5486,34 +5486,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464528</v>
+        <v>464557</v>
       </c>
       <c r="R47" t="n">
-        <v>6784961</v>
+        <v>6784931</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5556,6 +5561,11 @@
       <c r="AB47" t="inlineStr">
         <is>
           <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5582,10 +5592,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126602338</v>
+        <v>126602534</v>
       </c>
       <c r="B48" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5593,39 +5603,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464557</v>
+        <v>464528</v>
       </c>
       <c r="R48" t="n">
-        <v>6784931</v>
+        <v>6784961</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5668,11 +5673,6 @@
       <c r="AB48" t="inlineStr">
         <is>
           <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5806,10 +5806,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126601811</v>
+        <v>126601626</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5817,21 +5817,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5841,10 +5841,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464636</v>
+        <v>464649</v>
       </c>
       <c r="R50" t="n">
-        <v>6784853</v>
+        <v>6784788</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5913,7 +5913,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126602170</v>
+        <v>126601811</v>
       </c>
       <c r="B51" t="n">
         <v>79014</v>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464599</v>
+        <v>464636</v>
       </c>
       <c r="R51" t="n">
-        <v>6784887</v>
+        <v>6784853</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6020,10 +6020,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126601626</v>
+        <v>126602170</v>
       </c>
       <c r="B52" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6031,21 +6031,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6055,10 +6055,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464649</v>
+        <v>464599</v>
       </c>
       <c r="R52" t="n">
-        <v>6784788</v>
+        <v>6784887</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6090,7 +6090,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6127,10 +6127,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126602285</v>
+        <v>126601513</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6138,21 +6138,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6162,13 +6162,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464576</v>
+        <v>464648</v>
       </c>
       <c r="R53" t="n">
-        <v>6784903</v>
+        <v>6784781</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6234,10 +6234,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126601513</v>
+        <v>126602285</v>
       </c>
       <c r="B54" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6245,21 +6245,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6269,13 +6269,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464648</v>
+        <v>464576</v>
       </c>
       <c r="R54" t="n">
-        <v>6784781</v>
+        <v>6784903</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6341,7 +6341,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126601664</v>
+        <v>126601634</v>
       </c>
       <c r="B55" t="n">
         <v>79014</v>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464646</v>
+        <v>464649</v>
       </c>
       <c r="R55" t="n">
-        <v>6784794</v>
+        <v>6784788</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6448,7 +6448,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126601634</v>
+        <v>126601664</v>
       </c>
       <c r="B56" t="n">
         <v>79014</v>
@@ -6483,10 +6483,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464649</v>
+        <v>464646</v>
       </c>
       <c r="R56" t="n">
-        <v>6784788</v>
+        <v>6784794</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7324,32 +7324,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126602400</v>
+        <v>126601623</v>
       </c>
       <c r="B64" t="n">
-        <v>8447</v>
+        <v>79603</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7359,10 +7359,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464557</v>
+        <v>464649</v>
       </c>
       <c r="R64" t="n">
-        <v>6784931</v>
+        <v>6784788</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7431,32 +7431,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126601623</v>
+        <v>126602400</v>
       </c>
       <c r="B65" t="n">
-        <v>79603</v>
+        <v>8447</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464649</v>
+        <v>464557</v>
       </c>
       <c r="R65" t="n">
-        <v>6784788</v>
+        <v>6784931</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -5806,10 +5806,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126601626</v>
+        <v>126601811</v>
       </c>
       <c r="B50" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5817,21 +5817,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5841,10 +5841,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464649</v>
+        <v>464636</v>
       </c>
       <c r="R50" t="n">
-        <v>6784788</v>
+        <v>6784853</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5913,7 +5913,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126601811</v>
+        <v>126602170</v>
       </c>
       <c r="B51" t="n">
         <v>79014</v>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464636</v>
+        <v>464599</v>
       </c>
       <c r="R51" t="n">
-        <v>6784853</v>
+        <v>6784887</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6020,10 +6020,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126602170</v>
+        <v>126601626</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6031,21 +6031,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6055,10 +6055,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464599</v>
+        <v>464649</v>
       </c>
       <c r="R52" t="n">
-        <v>6784887</v>
+        <v>6784788</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6090,7 +6090,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6993,32 +6993,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126601627</v>
+        <v>126601826</v>
       </c>
       <c r="B61" t="n">
-        <v>78772</v>
+        <v>8447</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464649</v>
+        <v>464636</v>
       </c>
       <c r="R61" t="n">
-        <v>6784788</v>
+        <v>6784853</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7100,32 +7100,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126601826</v>
+        <v>126601627</v>
       </c>
       <c r="B62" t="n">
-        <v>8447</v>
+        <v>78772</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464636</v>
+        <v>464649</v>
       </c>
       <c r="R62" t="n">
-        <v>6784853</v>
+        <v>6784788</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8457,6 +8457,111 @@
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127465502</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>464662</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6785158</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -8462,7 +8462,7 @@
         <v>127465502</v>
       </c>
       <c r="B75" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -8462,7 +8462,7 @@
         <v>127465502</v>
       </c>
       <c r="B75" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -8462,7 +8462,7 @@
         <v>127465502</v>
       </c>
       <c r="B75" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -8462,7 +8462,7 @@
         <v>127465502</v>
       </c>
       <c r="B75" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -4393,7 +4393,7 @@
         <v>126592039</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>126591692</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>126602281</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>126601759</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>126602700</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>126602311</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126601678</v>
+        <v>126601839</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464640</v>
+        <v>464633</v>
       </c>
       <c r="R44" t="n">
-        <v>6784813</v>
+        <v>6784875</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5261,10 +5261,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126601839</v>
+        <v>126601678</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464633</v>
+        <v>464640</v>
       </c>
       <c r="R45" t="n">
-        <v>6784875</v>
+        <v>6784813</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5475,10 +5475,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126602338</v>
+        <v>126602534</v>
       </c>
       <c r="B47" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5486,39 +5486,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464557</v>
+        <v>464528</v>
       </c>
       <c r="R47" t="n">
-        <v>6784931</v>
+        <v>6784961</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5561,11 +5556,6 @@
       <c r="AB47" t="inlineStr">
         <is>
           <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5592,10 +5582,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126602534</v>
+        <v>126602338</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5603,34 +5593,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464528</v>
+        <v>464557</v>
       </c>
       <c r="R48" t="n">
-        <v>6784961</v>
+        <v>6784931</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5673,6 +5668,11 @@
       <c r="AB48" t="inlineStr">
         <is>
           <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5702,7 +5702,7 @@
         <v>126601621</v>
       </c>
       <c r="B49" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>126601811</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>126602170</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>126601626</v>
       </c>
       <c r="B52" t="n">
-        <v>78773</v>
+        <v>78770</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6127,10 +6127,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126601513</v>
+        <v>126602285</v>
       </c>
       <c r="B53" t="n">
-        <v>79632</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6138,21 +6138,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6162,13 +6162,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464648</v>
+        <v>464576</v>
       </c>
       <c r="R53" t="n">
-        <v>6784781</v>
+        <v>6784903</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6234,10 +6234,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126602285</v>
+        <v>126601513</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>79629</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6245,21 +6245,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6269,13 +6269,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464576</v>
+        <v>464648</v>
       </c>
       <c r="R54" t="n">
-        <v>6784903</v>
+        <v>6784781</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6341,10 +6341,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126601634</v>
+        <v>126601664</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464649</v>
+        <v>464646</v>
       </c>
       <c r="R55" t="n">
-        <v>6784788</v>
+        <v>6784794</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6448,10 +6448,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126601664</v>
+        <v>126601634</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6483,10 +6483,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464646</v>
+        <v>464649</v>
       </c>
       <c r="R56" t="n">
-        <v>6784794</v>
+        <v>6784788</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6670,7 +6670,7 @@
         <v>126601794</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>126601871</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>126602457</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6993,32 +6993,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126601826</v>
+        <v>126601627</v>
       </c>
       <c r="B61" t="n">
-        <v>8447</v>
+        <v>78769</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464636</v>
+        <v>464649</v>
       </c>
       <c r="R61" t="n">
-        <v>6784853</v>
+        <v>6784788</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7100,32 +7100,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126601627</v>
+        <v>126601826</v>
       </c>
       <c r="B62" t="n">
-        <v>78772</v>
+        <v>8447</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464649</v>
+        <v>464636</v>
       </c>
       <c r="R62" t="n">
-        <v>6784788</v>
+        <v>6784853</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7324,32 +7324,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126601623</v>
+        <v>126602400</v>
       </c>
       <c r="B64" t="n">
-        <v>79603</v>
+        <v>8447</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7359,10 +7359,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464649</v>
+        <v>464557</v>
       </c>
       <c r="R64" t="n">
-        <v>6784788</v>
+        <v>6784931</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7431,32 +7431,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126602400</v>
+        <v>126601623</v>
       </c>
       <c r="B65" t="n">
-        <v>8447</v>
+        <v>79600</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464557</v>
+        <v>464649</v>
       </c>
       <c r="R65" t="n">
-        <v>6784931</v>
+        <v>6784788</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7541,7 +7541,7 @@
         <v>126636587</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>126636762</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>126636699</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>126636748</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>126636724</v>
       </c>
       <c r="B71" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>126636906</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>126591818</v>
       </c>
       <c r="B74" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -4393,7 +4393,7 @@
         <v>126592039</v>
       </c>
       <c r="B37" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>126591692</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>126602281</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>126601759</v>
       </c>
       <c r="B40" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>126602700</v>
       </c>
       <c r="B42" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>126602311</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126601839</v>
+        <v>126601678</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464633</v>
+        <v>464640</v>
       </c>
       <c r="R44" t="n">
-        <v>6784875</v>
+        <v>6784813</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5261,10 +5261,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126601678</v>
+        <v>126601839</v>
       </c>
       <c r="B45" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464640</v>
+        <v>464633</v>
       </c>
       <c r="R45" t="n">
-        <v>6784813</v>
+        <v>6784875</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5475,10 +5475,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126602534</v>
+        <v>126602338</v>
       </c>
       <c r="B47" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5486,34 +5486,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464528</v>
+        <v>464557</v>
       </c>
       <c r="R47" t="n">
-        <v>6784961</v>
+        <v>6784931</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5556,6 +5561,11 @@
       <c r="AB47" t="inlineStr">
         <is>
           <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5582,10 +5592,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126602338</v>
+        <v>126602534</v>
       </c>
       <c r="B48" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5593,39 +5603,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464557</v>
+        <v>464528</v>
       </c>
       <c r="R48" t="n">
-        <v>6784931</v>
+        <v>6784961</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5668,11 +5673,6 @@
       <c r="AB48" t="inlineStr">
         <is>
           <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5702,7 +5702,7 @@
         <v>126601621</v>
       </c>
       <c r="B49" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>126601811</v>
       </c>
       <c r="B50" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>126602170</v>
       </c>
       <c r="B51" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>126601626</v>
       </c>
       <c r="B52" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6127,10 +6127,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126602285</v>
+        <v>126601513</v>
       </c>
       <c r="B53" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6138,21 +6138,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6162,13 +6162,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464576</v>
+        <v>464648</v>
       </c>
       <c r="R53" t="n">
-        <v>6784903</v>
+        <v>6784781</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6234,10 +6234,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126601513</v>
+        <v>126602285</v>
       </c>
       <c r="B54" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6245,21 +6245,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6269,13 +6269,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464648</v>
+        <v>464576</v>
       </c>
       <c r="R54" t="n">
-        <v>6784781</v>
+        <v>6784903</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6341,10 +6341,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126601664</v>
+        <v>126601634</v>
       </c>
       <c r="B55" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464646</v>
+        <v>464649</v>
       </c>
       <c r="R55" t="n">
-        <v>6784794</v>
+        <v>6784788</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6448,10 +6448,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126601634</v>
+        <v>126601664</v>
       </c>
       <c r="B56" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6483,10 +6483,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464649</v>
+        <v>464646</v>
       </c>
       <c r="R56" t="n">
-        <v>6784788</v>
+        <v>6784794</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6670,7 +6670,7 @@
         <v>126601794</v>
       </c>
       <c r="B58" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>126601871</v>
       </c>
       <c r="B59" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>126602457</v>
       </c>
       <c r="B60" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6993,32 +6993,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126601627</v>
+        <v>126601826</v>
       </c>
       <c r="B61" t="n">
-        <v>78769</v>
+        <v>8447</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464649</v>
+        <v>464636</v>
       </c>
       <c r="R61" t="n">
-        <v>6784788</v>
+        <v>6784853</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7100,32 +7100,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126601826</v>
+        <v>126601627</v>
       </c>
       <c r="B62" t="n">
-        <v>8447</v>
+        <v>78772</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464636</v>
+        <v>464649</v>
       </c>
       <c r="R62" t="n">
-        <v>6784853</v>
+        <v>6784788</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7324,32 +7324,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126602400</v>
+        <v>126601623</v>
       </c>
       <c r="B64" t="n">
-        <v>8447</v>
+        <v>79603</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7359,10 +7359,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464557</v>
+        <v>464649</v>
       </c>
       <c r="R64" t="n">
-        <v>6784931</v>
+        <v>6784788</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7431,32 +7431,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126601623</v>
+        <v>126602400</v>
       </c>
       <c r="B65" t="n">
-        <v>79600</v>
+        <v>8447</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464649</v>
+        <v>464557</v>
       </c>
       <c r="R65" t="n">
-        <v>6784788</v>
+        <v>6784931</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7541,7 +7541,7 @@
         <v>126636587</v>
       </c>
       <c r="B66" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>126636762</v>
       </c>
       <c r="B67" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>126636699</v>
       </c>
       <c r="B68" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>126636748</v>
       </c>
       <c r="B69" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>126636724</v>
       </c>
       <c r="B71" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>126636906</v>
       </c>
       <c r="B72" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>126591818</v>
       </c>
       <c r="B74" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126330908</v>
+        <v>126331429</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464517</v>
+        <v>464684</v>
       </c>
       <c r="R2" t="n">
-        <v>6784987</v>
+        <v>6784961</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126331429</v>
+        <v>126487082</v>
       </c>
       <c r="B3" t="n">
-        <v>79012</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464684</v>
+        <v>464562</v>
       </c>
       <c r="R3" t="n">
-        <v>6784961</v>
+        <v>6785102</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126330993</v>
+        <v>126487763</v>
       </c>
       <c r="B4" t="n">
-        <v>78739</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464525</v>
+        <v>464717</v>
       </c>
       <c r="R4" t="n">
-        <v>6784977</v>
+        <v>6784938</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +944,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,60 +974,63 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126330884</v>
+        <v>126492770</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464495</v>
+        <v>464734</v>
       </c>
       <c r="R5" t="n">
-        <v>6784979</v>
+        <v>6784881</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1031,12 +1054,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1045,28 +1073,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126331162</v>
+        <v>126492793</v>
       </c>
       <c r="B6" t="n">
-        <v>79598</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,37 +1103,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464525</v>
+        <v>464714</v>
       </c>
       <c r="R6" t="n">
-        <v>6784977</v>
+        <v>6784832</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1128,12 +1160,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1142,28 +1179,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126330861</v>
+        <v>126492867</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,37 +1209,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464495</v>
+        <v>464677</v>
       </c>
       <c r="R7" t="n">
-        <v>6784979</v>
+        <v>6785000</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1225,12 +1266,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1239,28 +1285,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126330962</v>
+        <v>126492915</v>
       </c>
       <c r="B8" t="n">
-        <v>79569</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,37 +1315,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464525</v>
+        <v>464647</v>
       </c>
       <c r="R8" t="n">
-        <v>6784977</v>
+        <v>6785005</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1322,12 +1372,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1336,50 +1391,51 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126488981</v>
+        <v>126330861</v>
       </c>
       <c r="B9" t="n">
-        <v>78738</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464546</v>
+        <v>464495</v>
       </c>
       <c r="R9" t="n">
-        <v>6785003</v>
+        <v>6784979</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1419,22 +1475,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,32 +1507,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126487403</v>
+        <v>126330895</v>
       </c>
       <c r="B10" t="n">
-        <v>75075</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464751</v>
+        <v>464517</v>
       </c>
       <c r="R10" t="n">
-        <v>6784883</v>
+        <v>6784987</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1526,22 +1572,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,14 +1604,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126487574</v>
+        <v>126487034</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1603,13 +1639,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464728</v>
+        <v>464717</v>
       </c>
       <c r="R11" t="n">
-        <v>6784927</v>
+        <v>6784886</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1649,6 +1685,11 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt i synfältet i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,53 +1716,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126487283</v>
+        <v>126487574</v>
       </c>
       <c r="B12" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464756</v>
+        <v>464728</v>
       </c>
       <c r="R12" t="n">
-        <v>6784907</v>
+        <v>6784927</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1750,7 +1786,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1760,7 +1796,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1775,63 +1811,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126492867</v>
+        <v>126487646</v>
       </c>
       <c r="B13" t="n">
-        <v>79012</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464677</v>
+        <v>464716</v>
       </c>
       <c r="R13" t="n">
-        <v>6785000</v>
+        <v>6784948</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1858,14 +1891,19 @@
           <t>2025-07-07</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1874,67 +1912,66 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126488269</v>
+        <v>126487746</v>
       </c>
       <c r="B14" t="n">
-        <v>78738</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464700</v>
+        <v>464684</v>
       </c>
       <c r="R14" t="n">
-        <v>6784944</v>
+        <v>6784934</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1963,7 +2000,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1973,7 +2010,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1988,62 +2030,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126489147</v>
+        <v>126487998</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464662</v>
+        <v>464676</v>
       </c>
       <c r="R15" t="n">
-        <v>6784965</v>
+        <v>6784994</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2075,7 +2112,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2085,7 +2122,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2100,44 +2137,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126488330</v>
+        <v>126488129</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2147,10 +2184,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464560</v>
+        <v>464617</v>
       </c>
       <c r="R16" t="n">
-        <v>6785003</v>
+        <v>6785002</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,51 +2256,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126492770</v>
+        <v>126488197</v>
       </c>
       <c r="B17" t="n">
-        <v>79012</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464734</v>
+        <v>464601</v>
       </c>
       <c r="R17" t="n">
-        <v>6784881</v>
+        <v>6785020</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2290,14 +2324,19 @@
           <t>2025-07-07</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2306,69 +2345,63 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126487945</v>
+        <v>126590840</v>
       </c>
       <c r="B18" t="n">
-        <v>57654</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464676</v>
+        <v>464734</v>
       </c>
       <c r="R18" t="n">
-        <v>6784994</v>
+        <v>6784815</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2395,22 +2428,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2437,45 +2470,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126488376</v>
+        <v>126590850</v>
       </c>
       <c r="B19" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464662</v>
+        <v>464724</v>
       </c>
       <c r="R19" t="n">
-        <v>6784965</v>
+        <v>6784810</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,22 +2535,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2532,26 +2565,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126487034</v>
+        <v>126590867</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2579,13 +2612,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464717</v>
+        <v>464730</v>
       </c>
       <c r="R20" t="n">
-        <v>6784886</v>
+        <v>6784826</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2609,27 +2642,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt i synfältet i en radie av ca 50 meter</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2656,51 +2684,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126492793</v>
+        <v>126591007</v>
       </c>
       <c r="B21" t="n">
-        <v>79012</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464714</v>
+        <v>464744</v>
       </c>
       <c r="R21" t="n">
-        <v>6784832</v>
+        <v>6784847</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2724,17 +2749,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2743,64 +2773,63 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126487763</v>
+        <v>126591506</v>
       </c>
       <c r="B22" t="n">
-        <v>79012</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464717</v>
+        <v>464757</v>
       </c>
       <c r="R22" t="n">
-        <v>6784938</v>
+        <v>6784856</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,22 +2856,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2857,26 +2886,26 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126488129</v>
+        <v>126591615</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2904,10 +2933,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464617</v>
+        <v>464711</v>
       </c>
       <c r="R23" t="n">
-        <v>6785002</v>
+        <v>6784812</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,22 +2963,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2976,32 +3005,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126486167</v>
+        <v>126591669</v>
       </c>
       <c r="B24" t="n">
-        <v>97245</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3011,10 +3040,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464730</v>
+        <v>464670</v>
       </c>
       <c r="R24" t="n">
-        <v>6784881</v>
+        <v>6784832</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,22 +3070,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3083,50 +3112,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126488274</v>
+        <v>126592039</v>
       </c>
       <c r="B25" t="n">
-        <v>57654</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464590</v>
+        <v>464676</v>
       </c>
       <c r="R25" t="n">
-        <v>6785034</v>
+        <v>6784794</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3153,22 +3177,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3195,32 +3219,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126488973</v>
+        <v>126592098</v>
       </c>
       <c r="B26" t="n">
-        <v>79598</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3230,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464546</v>
+        <v>464676</v>
       </c>
       <c r="R26" t="n">
-        <v>6785003</v>
+        <v>6784780</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3260,22 +3284,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Garn vid rullstensås</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3302,14 +3331,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126487646</v>
+        <v>126601634</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3337,10 +3366,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464716</v>
+        <v>464649</v>
       </c>
       <c r="R27" t="n">
-        <v>6784948</v>
+        <v>6784788</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3367,22 +3396,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3409,14 +3438,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126488197</v>
+        <v>126601664</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3444,10 +3473,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464601</v>
+        <v>464646</v>
       </c>
       <c r="R28" t="n">
-        <v>6785020</v>
+        <v>6784794</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3474,22 +3503,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3516,51 +3545,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126492915</v>
+        <v>126601674</v>
       </c>
       <c r="B29" t="n">
-        <v>79012</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464647</v>
+        <v>464640</v>
       </c>
       <c r="R29" t="n">
-        <v>6785005</v>
+        <v>6784813</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3584,17 +3610,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3603,64 +3634,63 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126487777</v>
+        <v>126601759</v>
       </c>
       <c r="B30" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464717</v>
+        <v>464631</v>
       </c>
       <c r="R30" t="n">
-        <v>6784938</v>
+        <v>6784825</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3687,22 +3717,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3717,26 +3747,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126487998</v>
+        <v>126601794</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3764,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464676</v>
+        <v>464632</v>
       </c>
       <c r="R31" t="n">
-        <v>6784994</v>
+        <v>6784828</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3794,22 +3824,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3836,14 +3866,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126487746</v>
+        <v>126601811</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3871,13 +3901,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464684</v>
+        <v>464636</v>
       </c>
       <c r="R32" t="n">
-        <v>6784934</v>
+        <v>6784853</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3901,27 +3931,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3948,32 +3973,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126487596</v>
+        <v>126601839</v>
       </c>
       <c r="B33" t="n">
-        <v>75075</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3983,10 +4008,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464738</v>
+        <v>464633</v>
       </c>
       <c r="R33" t="n">
-        <v>6784934</v>
+        <v>6784875</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4013,22 +4038,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4055,53 +4080,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126487352</v>
+        <v>126601871</v>
       </c>
       <c r="B34" t="n">
-        <v>57654</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464756</v>
+        <v>464603</v>
       </c>
       <c r="R34" t="n">
-        <v>6784907</v>
+        <v>6784862</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4125,22 +4145,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4155,69 +4175,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126487908</v>
+        <v>126602170</v>
       </c>
       <c r="B35" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464652</v>
+        <v>464599</v>
       </c>
       <c r="R35" t="n">
-        <v>6784976</v>
+        <v>6784887</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4241,22 +4252,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4271,44 +4282,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126488040</v>
+        <v>126602281</v>
       </c>
       <c r="B36" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4318,10 +4329,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464676</v>
+        <v>464586</v>
       </c>
       <c r="R36" t="n">
-        <v>6784994</v>
+        <v>6784897</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4348,22 +4359,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,14 +4401,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126592039</v>
+        <v>126602285</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4425,10 +4436,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464676</v>
+        <v>464576</v>
       </c>
       <c r="R37" t="n">
-        <v>6784794</v>
+        <v>6784903</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4455,22 +4466,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,14 +4508,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126591692</v>
+        <v>126602311</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4532,10 +4543,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464670</v>
+        <v>464557</v>
       </c>
       <c r="R38" t="n">
-        <v>6784832</v>
+        <v>6784931</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4562,22 +4573,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Miljöbild, torraka i bakgrund</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4604,14 +4620,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126602281</v>
+        <v>126602457</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4639,10 +4655,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464586</v>
+        <v>464554</v>
       </c>
       <c r="R39" t="n">
-        <v>6784897</v>
+        <v>6784937</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4685,6 +4701,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Miljöbild, torraka i bakgrund</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4711,14 +4732,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126601759</v>
+        <v>126602534</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4746,10 +4767,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464631</v>
+        <v>464528</v>
       </c>
       <c r="R40" t="n">
-        <v>6784825</v>
+        <v>6784961</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4818,32 +4839,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126602799</v>
+        <v>126602593</v>
       </c>
       <c r="B41" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4874,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464491</v>
+        <v>464508</v>
       </c>
       <c r="R41" t="n">
-        <v>6784992</v>
+        <v>6784966</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4899,11 +4920,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Miljöbild med torraka och bandad tall med garnlav bakgrund</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4933,11 +4949,11 @@
         <v>126602700</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5042,14 +5058,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126602311</v>
+        <v>126602820</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5077,10 +5093,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464557</v>
+        <v>464494</v>
       </c>
       <c r="R43" t="n">
-        <v>6784931</v>
+        <v>6785014</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5123,11 +5139,6 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Miljöbild, torraka i bakgrund</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5154,14 +5165,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126601678</v>
+        <v>126602970</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5189,10 +5200,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464640</v>
+        <v>464508</v>
       </c>
       <c r="R44" t="n">
-        <v>6784813</v>
+        <v>6785019</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5224,7 +5235,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5234,7 +5245,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5261,14 +5272,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126601839</v>
+        <v>126603485</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5296,10 +5307,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464633</v>
+        <v>464538</v>
       </c>
       <c r="R45" t="n">
-        <v>6784875</v>
+        <v>6785057</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5342,6 +5353,11 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Miljöbild med två tallar, garnlav samt torrakor</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5368,45 +5384,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126602177</v>
+        <v>126636587</v>
       </c>
       <c r="B46" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464599</v>
+        <v>464649</v>
       </c>
       <c r="R46" t="n">
-        <v>6784887</v>
+        <v>6784894</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5436,27 +5455,18 @@
           <t>2025-07-12</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>08:52</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-12</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>08:52</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5475,50 +5485,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126602338</v>
+        <v>126636699</v>
       </c>
       <c r="B47" t="n">
-        <v>57654</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464557</v>
+        <v>464636</v>
       </c>
       <c r="R47" t="n">
-        <v>6784931</v>
+        <v>6784910</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5548,32 +5556,18 @@
           <t>2025-07-12</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>08:52</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-12</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5592,14 +5586,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126602534</v>
+        <v>126636724</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5621,16 +5615,19 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464528</v>
+        <v>464637</v>
       </c>
       <c r="R48" t="n">
-        <v>6784961</v>
+        <v>6784913</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5660,27 +5657,18 @@
           <t>2025-07-12</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>08:52</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-12</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>08:52</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5699,45 +5687,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126601621</v>
+        <v>126636748</v>
       </c>
       <c r="B49" t="n">
-        <v>79632</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464649</v>
+        <v>464639</v>
       </c>
       <c r="R49" t="n">
-        <v>6784788</v>
+        <v>6784929</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5767,27 +5758,18 @@
           <t>2025-07-12</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>08:25</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-12</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>08:25</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5806,14 +5788,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126601811</v>
+        <v>126636762</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5835,16 +5817,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464636</v>
+        <v>464639</v>
       </c>
       <c r="R50" t="n">
-        <v>6784853</v>
+        <v>6784932</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5874,27 +5859,18 @@
           <t>2025-07-12</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>08:52</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-12</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>08:52</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5913,14 +5889,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126602170</v>
+        <v>126636906</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5942,16 +5918,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464599</v>
+        <v>464593</v>
       </c>
       <c r="R51" t="n">
-        <v>6784887</v>
+        <v>6785029</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5981,27 +5960,18 @@
           <t>2025-07-12</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>08:52</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-12</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>08:52</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6020,10 +5990,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126601626</v>
+        <v>126487403</v>
       </c>
       <c r="B52" t="n">
-        <v>78773</v>
+        <v>83307</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6031,21 +6001,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6055,10 +6025,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464649</v>
+        <v>464751</v>
       </c>
       <c r="R52" t="n">
-        <v>6784788</v>
+        <v>6784883</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6085,22 +6055,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6127,10 +6097,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126601513</v>
+        <v>126487596</v>
       </c>
       <c r="B53" t="n">
-        <v>79632</v>
+        <v>83307</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6138,21 +6108,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6162,13 +6132,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464648</v>
+        <v>464738</v>
       </c>
       <c r="R53" t="n">
-        <v>6784781</v>
+        <v>6784934</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6192,22 +6162,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6234,10 +6204,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126602285</v>
+        <v>127465540</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>83307</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6245,34 +6215,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464576</v>
+        <v>464659</v>
       </c>
       <c r="R54" t="n">
-        <v>6784903</v>
+        <v>6785196</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6299,22 +6272,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>08:52</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>08:52</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6323,6 +6286,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6341,10 +6305,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126601634</v>
+        <v>126488269</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6352,37 +6316,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464649</v>
+        <v>464700</v>
       </c>
       <c r="R55" t="n">
-        <v>6784788</v>
+        <v>6784944</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6406,22 +6370,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6436,22 +6400,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126601664</v>
+        <v>126488981</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>79084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6459,21 +6423,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6483,10 +6447,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464646</v>
+        <v>464546</v>
       </c>
       <c r="R56" t="n">
-        <v>6784794</v>
+        <v>6785003</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6513,22 +6477,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6555,32 +6519,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126602528</v>
+        <v>126601627</v>
       </c>
       <c r="B57" t="n">
-        <v>8447</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6590,10 +6554,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464528</v>
+        <v>464649</v>
       </c>
       <c r="R57" t="n">
-        <v>6784961</v>
+        <v>6784788</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6625,7 +6589,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6635,12 +6599,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Miljöbild, flera torrakor i bild</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6667,10 +6626,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126601794</v>
+        <v>126602948</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6678,21 +6637,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6702,10 +6661,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464632</v>
+        <v>464508</v>
       </c>
       <c r="R58" t="n">
-        <v>6784828</v>
+        <v>6785019</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6774,10 +6733,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126601871</v>
+        <v>126330969</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>79946</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6785,21 +6744,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6809,10 +6768,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464603</v>
+        <v>464525</v>
       </c>
       <c r="R59" t="n">
-        <v>6784862</v>
+        <v>6784977</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6839,22 +6798,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>08:52</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>08:52</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6881,10 +6830,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126602457</v>
+        <v>126488973</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>79946</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6892,21 +6841,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6916,10 +6865,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464554</v>
+        <v>464546</v>
       </c>
       <c r="R60" t="n">
-        <v>6784937</v>
+        <v>6785003</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6946,27 +6895,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Miljöbild, torraka i bakgrund</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6993,32 +6937,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126601826</v>
+        <v>126591818</v>
       </c>
       <c r="B61" t="n">
-        <v>8447</v>
+        <v>79946</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7028,10 +6972,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464636</v>
+        <v>464670</v>
       </c>
       <c r="R61" t="n">
-        <v>6784853</v>
+        <v>6784832</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7058,22 +7002,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7100,10 +7044,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126601627</v>
+        <v>126601513</v>
       </c>
       <c r="B62" t="n">
-        <v>78772</v>
+        <v>79946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7111,21 +7055,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7135,13 +7079,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464649</v>
+        <v>464648</v>
       </c>
       <c r="R62" t="n">
-        <v>6784788</v>
+        <v>6784781</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7207,10 +7151,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126602005</v>
+        <v>126601621</v>
       </c>
       <c r="B63" t="n">
-        <v>57654</v>
+        <v>79946</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7218,39 +7162,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>464603</v>
+        <v>464649</v>
       </c>
       <c r="R63" t="n">
-        <v>6784862</v>
+        <v>6784788</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7282,7 +7221,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7292,12 +7231,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Miljöbild på hackhål/bohål</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7324,10 +7258,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126601623</v>
+        <v>126602950</v>
       </c>
       <c r="B64" t="n">
-        <v>79603</v>
+        <v>79946</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7335,21 +7269,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7359,10 +7293,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464649</v>
+        <v>464508</v>
       </c>
       <c r="R64" t="n">
-        <v>6784788</v>
+        <v>6785019</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7394,7 +7328,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7404,7 +7338,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7431,10 +7365,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126602400</v>
+        <v>126487352</v>
       </c>
       <c r="B65" t="n">
-        <v>8447</v>
+        <v>57950</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7442,37 +7376,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464557</v>
+        <v>464756</v>
       </c>
       <c r="R65" t="n">
-        <v>6784931</v>
+        <v>6784907</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7496,22 +7435,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7526,60 +7465,62 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126636587</v>
+        <v>126487945</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>57950</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464649</v>
+        <v>464676</v>
       </c>
       <c r="R66" t="n">
-        <v>6784894</v>
+        <v>6784994</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7606,12 +7547,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7620,7 +7571,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7639,48 +7589,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126636762</v>
+        <v>126488274</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>57950</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464639</v>
+        <v>464590</v>
       </c>
       <c r="R67" t="n">
-        <v>6784932</v>
+        <v>6785034</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7707,12 +7659,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7721,7 +7683,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7740,48 +7701,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126636699</v>
+        <v>126601937</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>57950</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464636</v>
+        <v>464603</v>
       </c>
       <c r="R68" t="n">
-        <v>6784910</v>
+        <v>6784862</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7811,18 +7774,32 @@
           <t>2025-07-12</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-12</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Miljöbilder på bohål</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7841,48 +7818,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126636748</v>
+        <v>126602338</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>57950</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464639</v>
+        <v>464557</v>
       </c>
       <c r="R69" t="n">
-        <v>6784929</v>
+        <v>6784931</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7912,18 +7891,32 @@
           <t>2025-07-12</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-12</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7942,10 +7935,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126636650</v>
+        <v>126636895</v>
       </c>
       <c r="B70" t="n">
-        <v>8447</v>
+        <v>57950</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7953,28 +7946,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7982,10 +7978,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464649</v>
+        <v>464593</v>
       </c>
       <c r="R70" t="n">
-        <v>6784894</v>
+        <v>6785029</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8026,7 +8022,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8045,37 +8040,42 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126636724</v>
+        <v>126671230</v>
       </c>
       <c r="B71" t="n">
-        <v>79014</v>
+        <v>57950</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464637</v>
+        <v>464649</v>
       </c>
       <c r="R71" t="n">
-        <v>6784913</v>
+        <v>6785183</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8127,7 +8127,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8146,37 +8145,42 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126636906</v>
+        <v>127465306</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>57950</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8184,10 +8188,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464593</v>
+        <v>464656</v>
       </c>
       <c r="R72" t="n">
-        <v>6785029</v>
+        <v>6785173</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8214,12 +8218,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8228,7 +8232,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8247,14 +8250,14 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126636895</v>
+        <v>127465502</v>
       </c>
       <c r="B73" t="n">
-        <v>57654</v>
+        <v>57950</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -8280,7 +8283,7 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -8290,10 +8293,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464593</v>
+        <v>464662</v>
       </c>
       <c r="R73" t="n">
-        <v>6785029</v>
+        <v>6785158</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8320,12 +8323,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8352,45 +8355,53 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126591818</v>
+        <v>127465578</v>
       </c>
       <c r="B74" t="n">
-        <v>79632</v>
+        <v>57950</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464670</v>
+        <v>464659</v>
       </c>
       <c r="R74" t="n">
-        <v>6784832</v>
+        <v>6785196</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8417,22 +8428,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>17:39</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>17:39</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8459,10 +8460,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127465502</v>
+        <v>126487696</v>
       </c>
       <c r="B75" t="n">
-        <v>57669</v>
+        <v>58209</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8470,42 +8471,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>102980</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464662</v>
+        <v>464716</v>
       </c>
       <c r="R75" t="n">
-        <v>6785158</v>
+        <v>6784948</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8532,12 +8530,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8561,6 +8569,2471 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>126330884</v>
+      </c>
+      <c r="B76" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>464495</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6784979</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>126487283</v>
+      </c>
+      <c r="B77" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>464756</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6784907</v>
+      </c>
+      <c r="S77" t="n">
+        <v>20</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>126487777</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>464717</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6784938</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>126487908</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>464652</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6784976</v>
+      </c>
+      <c r="S79" t="n">
+        <v>20</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>126488040</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>464676</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6784994</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>126488330</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>464560</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6785003</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>126489147</v>
+      </c>
+      <c r="B82" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>464662</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6784965</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>126601826</v>
+      </c>
+      <c r="B83" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>464636</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6784853</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>126602177</v>
+      </c>
+      <c r="B84" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>464599</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6784887</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>126602400</v>
+      </c>
+      <c r="B85" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>464557</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6784931</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>126602528</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>464528</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6784961</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Miljöbild, flera torrakor i bild</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>126602588</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>464508</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6784966</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>126602799</v>
+      </c>
+      <c r="B88" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>464491</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6784992</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Miljöbild med torraka och bandad tall med garnlav bakgrund</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>126603440</v>
+      </c>
+      <c r="B89" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>464529</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6785062</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Miljöbild på två lågor</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>126636650</v>
+      </c>
+      <c r="B90" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>464649</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6784894</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>126486167</v>
+      </c>
+      <c r="B91" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>464730</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6784881</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>126330993</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>464525</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6784977</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>126488376</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>464662</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6784965</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>126601626</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>464649</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6784788</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>126602944</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>464508</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6785019</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Miljöbild med kolad stubbe, bandad</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>126330962</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>464525</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6784977</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>126601623</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>464649</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6784788</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>126492848</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>464714</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6784906</v>
+      </c>
+      <c r="S98" t="n">
+        <v>25</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29934-2025 artfynd.xlsx
+++ b/artfynd/A 29934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY98"/>
+  <dimension ref="A1:AZ98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126331429</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487082</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487763</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126492770</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126492793</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126492867</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126492915</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126330861</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1601,6 +1646,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126330895</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1713,6 +1763,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487034</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1820,6 +1875,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487574</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1927,6 +1987,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487646</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2039,6 +2104,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487746</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2146,6 +2216,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487998</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2253,6 +2328,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126488129</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2360,6 +2440,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126488197</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2467,6 +2552,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590840</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2574,6 +2664,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590850</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2681,6 +2776,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590867</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2788,6 +2888,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591007</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2895,6 +3000,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591506</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3002,6 +3112,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591615</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3109,6 +3224,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591669</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3216,6 +3336,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126592039</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3328,6 +3453,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126592098</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3435,6 +3565,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601634</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3542,6 +3677,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601664</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3649,6 +3789,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601674</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3756,6 +3901,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601759</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3863,6 +4013,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601794</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3970,6 +4125,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601811</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4077,6 +4237,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601839</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4184,6 +4349,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601871</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4291,6 +4461,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602170</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4398,6 +4573,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602281</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4505,6 +4685,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602285</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4617,6 +4802,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602311</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4729,6 +4919,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602457</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4836,6 +5031,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602534</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4943,6 +5143,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602593</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5055,6 +5260,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602700</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5162,6 +5372,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602820</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5269,6 +5484,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602970</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5381,6 +5601,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126603485</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5482,6 +5707,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126636587</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5583,6 +5813,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126636699</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5684,6 +5919,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126636724</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5785,6 +6025,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126636748</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5886,6 +6131,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126636762</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5987,6 +6237,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126636906</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6094,6 +6349,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487403</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6201,6 +6461,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487596</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6302,6 +6567,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127465540</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6409,6 +6679,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126488269</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6516,6 +6791,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126488981</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6623,6 +6903,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601627</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6730,6 +7015,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602948</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6827,6 +7117,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126330969</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6934,6 +7229,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126488973</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7041,6 +7341,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126591818</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7148,6 +7453,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601513</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7255,6 +7565,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601621</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7362,6 +7677,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602950</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7474,6 +7794,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487352</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7586,6 +7911,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487945</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7698,6 +8028,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126488274</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7815,6 +8150,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601937</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7932,6 +8272,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602338</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8037,6 +8382,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126636895</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8142,6 +8492,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126671230</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8247,6 +8602,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127465306</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8352,6 +8712,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127465502</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8457,6 +8822,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127465578</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8569,6 +8939,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487696</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8666,6 +9041,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126330884</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8778,6 +9158,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487283</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8885,6 +9270,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487777</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9001,6 +9391,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487908</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9108,6 +9503,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126488040</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9215,6 +9615,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126488330</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9327,6 +9732,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126489147</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9434,6 +9844,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601826</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9541,6 +9956,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602177</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9648,6 +10068,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602400</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9760,6 +10185,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602528</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9867,6 +10297,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602588</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9979,6 +10414,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602799</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10091,6 +10531,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126603440</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10194,6 +10639,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126636650</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10301,6 +10751,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126486167</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10398,6 +10853,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126330993</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10505,6 +10965,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126488376</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10612,6 +11077,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601626</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10724,6 +11194,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126602944</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10821,6 +11296,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126330962</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10928,6 +11408,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601623</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11034,8 +11519,112 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126492848</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>